--- a/artfynd/A 65599-2021 artfynd.xlsx
+++ b/artfynd/A 65599-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65599-2021 artfynd.xlsx
+++ b/artfynd/A 65599-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>326413</v>
+        <v>16570611</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1143</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>LUGNET ST LÖPGÖL, Sm</t>
+          <t>St. Löpgöl., Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572529.785741954</v>
+        <v>572650</v>
       </c>
       <c r="R2" t="n">
-        <v>6450484.655956117</v>
+        <v>6450456</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +742,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-03-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-03-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Länsstyrelsens källa: k15e</t>
+          <t>400m SO</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,29 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grova ekar lövlund</t>
+          <t>skogsbryn</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ek</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>gammal ek</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -806,12 +793,7 @@
         <v>16570634</v>
       </c>
       <c r="B3" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572483.621494267</v>
+        <v>572484</v>
       </c>
       <c r="R3" t="n">
-        <v>6450437.935018161</v>
+        <v>6450438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +860,9 @@
           <t>2004-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-03-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -933,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16570629</v>
+        <v>621014</v>
       </c>
       <c r="B4" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,36 +916,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>1897</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St. Löpgöl., Sm</t>
+          <t>Stora Löpgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572483.621494267</v>
+        <v>572592</v>
       </c>
       <c r="R4" t="n">
-        <v>6450437.935018161</v>
+        <v>6450395</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,27 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-03-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-03-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>300m S</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,29 +998,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>lövskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>grov ek</t>
+          <t>gräsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Marie-Louise Fagerström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kjell Mathson</t>
+          <t>Marie-Louise Fagerström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1066,12 +1024,7 @@
         <v>16570627</v>
       </c>
       <c r="B5" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572509.335875825</v>
+        <v>572509</v>
       </c>
       <c r="R5" t="n">
-        <v>6450447.369757309</v>
+        <v>6450447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,19 +1091,9 @@
           <t>2004-03-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2004-03-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1193,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>621014</v>
+        <v>16570629</v>
       </c>
       <c r="B6" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,48 +1147,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1897</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Löpgöl, Sm</t>
+          <t>St. Löpgöl., Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572591.652304641</v>
+        <v>572484</v>
       </c>
       <c r="R6" t="n">
-        <v>6450395.089781982</v>
+        <v>6450438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,22 +1203,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-03-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-03-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>300m S</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,23 +1222,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gräsmark</t>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>grov ek</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie-Louise Fagerström</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie-Louise Fagerström</t>
+          <t>Kjell Mathson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 65599-2021 artfynd.xlsx
+++ b/artfynd/A 65599-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16570611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16570634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/621014</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16570627</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,8 +1273,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16570629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>